--- a/base_despesas/2025/despesas_202512.xlsx
+++ b/base_despesas/2025/despesas_202512.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -19275,7 +19275,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -19521,7 +19521,7 @@
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -19890,7 +19890,7 @@
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="AG159" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AG160" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -21120,7 +21120,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -21243,7 +21243,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="AG172" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="AG173" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -21858,7 +21858,7 @@
       </c>
       <c r="AG174" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -21981,7 +21981,7 @@
       </c>
       <c r="AG175" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22104,7 @@
       </c>
       <c r="AG176" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -22227,7 +22227,7 @@
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -22350,7 +22350,7 @@
       </c>
       <c r="AG178" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -22473,7 +22473,7 @@
       </c>
       <c r="AG179" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="AG180" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -22719,7 +22719,7 @@
       </c>
       <c r="AG181" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="AG182" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -22965,7 +22965,7 @@
       </c>
       <c r="AG183" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -23088,7 +23088,7 @@
       </c>
       <c r="AG184" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="AG185" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -23334,7 +23334,7 @@
       </c>
       <c r="AG186" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -23580,7 +23580,7 @@
       </c>
       <c r="AG188" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -23703,7 +23703,7 @@
       </c>
       <c r="AG189" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="AG190" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AG191" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -24072,7 +24072,7 @@
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -24195,7 +24195,7 @@
       </c>
       <c r="AG193" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="AG194" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -24441,7 +24441,7 @@
       </c>
       <c r="AG195" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -24564,7 +24564,7 @@
       </c>
       <c r="AG196" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="AG197" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -24810,7 +24810,7 @@
       </c>
       <c r="AG198" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="AG199" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="AG200" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="AG201" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -25302,7 +25302,7 @@
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -25425,7 +25425,7 @@
       </c>
       <c r="AG203" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -25548,7 +25548,7 @@
       </c>
       <c r="AG204" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -25671,7 +25671,7 @@
       </c>
       <c r="AG205" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AG206" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="AG208" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AG209" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -26286,7 +26286,7 @@
       </c>
       <c r="AG210" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
       </c>
       <c r="AG211" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -26532,7 +26532,7 @@
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="AG213" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -26778,7 +26778,7 @@
       </c>
       <c r="AG214" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -26901,7 +26901,7 @@
       </c>
       <c r="AG215" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27024,7 @@
       </c>
       <c r="AG216" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="AG217" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -27270,7 +27270,7 @@
       </c>
       <c r="AG218" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -27393,7 +27393,7 @@
       </c>
       <c r="AG219" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -27516,7 +27516,7 @@
       </c>
       <c r="AG220" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -27639,7 +27639,7 @@
       </c>
       <c r="AG221" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -27762,7 +27762,7 @@
       </c>
       <c r="AG222" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="AG223" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28008,7 +28008,7 @@
       </c>
       <c r="AG224" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28131,7 +28131,7 @@
       </c>
       <c r="AG225" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="AG226" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="AG227" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28500,7 +28500,7 @@
       </c>
       <c r="AG228" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28623,7 +28623,7 @@
       </c>
       <c r="AG229" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28746,7 +28746,7 @@
       </c>
       <c r="AG230" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
       </c>
       <c r="AG231" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -28992,7 +28992,7 @@
       </c>
       <c r="AG232" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -29115,7 +29115,7 @@
       </c>
       <c r="AG233" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="AG234" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="AG235" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -29484,7 +29484,7 @@
       </c>
       <c r="AG236" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -29607,7 +29607,7 @@
       </c>
       <c r="AG237" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="AG238" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="AG239" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="AG240" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -30099,7 +30099,7 @@
       </c>
       <c r="AG241" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -30222,7 +30222,7 @@
       </c>
       <c r="AG242" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -30345,7 +30345,7 @@
       </c>
       <c r="AG243" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="AG244" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -30591,7 +30591,7 @@
       </c>
       <c r="AG245" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -30714,7 +30714,7 @@
       </c>
       <c r="AG246" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -30837,7 +30837,7 @@
       </c>
       <c r="AG247" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -30960,7 +30960,7 @@
       </c>
       <c r="AG248" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -31083,7 +31083,7 @@
       </c>
       <c r="AG249" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="AG250" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -31329,7 +31329,7 @@
       </c>
       <c r="AG251" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="AG252" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="AG253" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -31698,7 +31698,7 @@
       </c>
       <c r="AG254" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -31821,7 +31821,7 @@
       </c>
       <c r="AG255" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -31944,7 +31944,7 @@
       </c>
       <c r="AG256" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -32067,7 +32067,7 @@
       </c>
       <c r="AG257" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -32190,7 +32190,7 @@
       </c>
       <c r="AG258" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -32313,7 +32313,7 @@
       </c>
       <c r="AG259" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -32436,7 +32436,7 @@
       </c>
       <c r="AG260" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="AG261" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="AG262" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="AG263" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AG264" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="AG265" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="AG266" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="AG267" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="AG268" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="AG269" t="inlineStr">
         <is>
-          <t>19/02/2026 16:10:04</t>
+          <t>20/02/2026 07:06:55</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2025/despesas_202512.xlsx
+++ b/base_despesas/2025/despesas_202512.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AG39" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="AG44" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="AG50" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AG55" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="AG60" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AG63" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AG64" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AG65" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AG68" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="AG69" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AG70" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="AG71" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AG73" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="AG83" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AG84" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AG86" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="AG88" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -11403,7 +11403,7 @@
       </c>
       <c r="AG89" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="AG90" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -11649,7 +11649,7 @@
       </c>
       <c r="AG91" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AG104" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="AG105" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="AG106" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13617,7 +13617,7 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="AG108" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="AG109" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -13986,7 +13986,7 @@
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14970,7 @@
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15216,7 @@
       </c>
       <c r="AG120" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15831,7 @@
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AG133" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="AG136" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AG138" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="AG139" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -18045,7 +18045,7 @@
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18291,7 @@
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -19029,7 +19029,7 @@
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -19275,7 +19275,7 @@
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -19398,7 +19398,7 @@
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -19521,7 +19521,7 @@
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -19890,7 +19890,7 @@
       </c>
       <c r="AG158" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20013,7 +20013,7 @@
       </c>
       <c r="AG159" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AG160" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20259,7 +20259,7 @@
       </c>
       <c r="AG161" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="AG163" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="AG164" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20751,7 +20751,7 @@
       </c>
       <c r="AG165" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -21120,7 +21120,7 @@
       </c>
       <c r="AG168" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -21243,7 +21243,7 @@
       </c>
       <c r="AG169" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -21366,7 +21366,7 @@
       </c>
       <c r="AG170" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="AG171" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
       </c>
       <c r="AG172" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="AG173" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -21858,7 +21858,7 @@
       </c>
       <c r="AG174" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -21981,7 +21981,7 @@
       </c>
       <c r="AG175" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22104,7 @@
       </c>
       <c r="AG176" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -22227,7 +22227,7 @@
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -22350,7 +22350,7 @@
       </c>
       <c r="AG178" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -22473,7 +22473,7 @@
       </c>
       <c r="AG179" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -22596,7 +22596,7 @@
       </c>
       <c r="AG180" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -22719,7 +22719,7 @@
       </c>
       <c r="AG181" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="AG182" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -22965,7 +22965,7 @@
       </c>
       <c r="AG183" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -23088,7 +23088,7 @@
       </c>
       <c r="AG184" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="AG185" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -23334,7 +23334,7 @@
       </c>
       <c r="AG186" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -23457,7 +23457,7 @@
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -23580,7 +23580,7 @@
       </c>
       <c r="AG188" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -23703,7 +23703,7 @@
       </c>
       <c r="AG189" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -23826,7 +23826,7 @@
       </c>
       <c r="AG190" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="AG191" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -24072,7 +24072,7 @@
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -24195,7 +24195,7 @@
       </c>
       <c r="AG193" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="AG194" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -24441,7 +24441,7 @@
       </c>
       <c r="AG195" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -24564,7 +24564,7 @@
       </c>
       <c r="AG196" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -24687,7 +24687,7 @@
       </c>
       <c r="AG197" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -24810,7 +24810,7 @@
       </c>
       <c r="AG198" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -24933,7 +24933,7 @@
       </c>
       <c r="AG199" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -25056,7 +25056,7 @@
       </c>
       <c r="AG200" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -25179,7 +25179,7 @@
       </c>
       <c r="AG201" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -25302,7 +25302,7 @@
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -25425,7 +25425,7 @@
       </c>
       <c r="AG203" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -25548,7 +25548,7 @@
       </c>
       <c r="AG204" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -25671,7 +25671,7 @@
       </c>
       <c r="AG205" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AG206" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26040,7 @@
       </c>
       <c r="AG208" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AG209" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -26286,7 +26286,7 @@
       </c>
       <c r="AG210" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26409,7 @@
       </c>
       <c r="AG211" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -26532,7 +26532,7 @@
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -26655,7 +26655,7 @@
       </c>
       <c r="AG213" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -26778,7 +26778,7 @@
       </c>
       <c r="AG214" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -26901,7 +26901,7 @@
       </c>
       <c r="AG215" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -27024,7 +27024,7 @@
       </c>
       <c r="AG216" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="AG217" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -27270,7 +27270,7 @@
       </c>
       <c r="AG218" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -27393,7 +27393,7 @@
       </c>
       <c r="AG219" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -27516,7 +27516,7 @@
       </c>
       <c r="AG220" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -27639,7 +27639,7 @@
       </c>
       <c r="AG221" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -27762,7 +27762,7 @@
       </c>
       <c r="AG222" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="AG223" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28008,7 +28008,7 @@
       </c>
       <c r="AG224" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28131,7 +28131,7 @@
       </c>
       <c r="AG225" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28254,7 +28254,7 @@
       </c>
       <c r="AG226" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28377,7 +28377,7 @@
       </c>
       <c r="AG227" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28500,7 +28500,7 @@
       </c>
       <c r="AG228" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28623,7 +28623,7 @@
       </c>
       <c r="AG229" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28746,7 +28746,7 @@
       </c>
       <c r="AG230" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
       </c>
       <c r="AG231" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -28992,7 +28992,7 @@
       </c>
       <c r="AG232" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -29115,7 +29115,7 @@
       </c>
       <c r="AG233" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -29238,7 +29238,7 @@
       </c>
       <c r="AG234" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="AG235" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -29484,7 +29484,7 @@
       </c>
       <c r="AG236" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -29607,7 +29607,7 @@
       </c>
       <c r="AG237" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="AG238" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -29853,7 +29853,7 @@
       </c>
       <c r="AG239" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -29976,7 +29976,7 @@
       </c>
       <c r="AG240" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -30099,7 +30099,7 @@
       </c>
       <c r="AG241" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -30222,7 +30222,7 @@
       </c>
       <c r="AG242" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -30345,7 +30345,7 @@
       </c>
       <c r="AG243" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -30468,7 +30468,7 @@
       </c>
       <c r="AG244" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -30591,7 +30591,7 @@
       </c>
       <c r="AG245" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -30714,7 +30714,7 @@
       </c>
       <c r="AG246" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -30837,7 +30837,7 @@
       </c>
       <c r="AG247" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -30960,7 +30960,7 @@
       </c>
       <c r="AG248" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -31083,7 +31083,7 @@
       </c>
       <c r="AG249" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="AG250" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -31329,7 +31329,7 @@
       </c>
       <c r="AG251" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -31452,7 +31452,7 @@
       </c>
       <c r="AG252" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -31575,7 +31575,7 @@
       </c>
       <c r="AG253" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -31698,7 +31698,7 @@
       </c>
       <c r="AG254" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -31821,7 +31821,7 @@
       </c>
       <c r="AG255" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -31944,7 +31944,7 @@
       </c>
       <c r="AG256" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -32067,7 +32067,7 @@
       </c>
       <c r="AG257" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -32190,7 +32190,7 @@
       </c>
       <c r="AG258" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -32313,7 +32313,7 @@
       </c>
       <c r="AG259" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -32436,7 +32436,7 @@
       </c>
       <c r="AG260" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -32559,7 +32559,7 @@
       </c>
       <c r="AG261" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -32682,7 +32682,7 @@
       </c>
       <c r="AG262" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -32805,7 +32805,7 @@
       </c>
       <c r="AG263" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -32928,7 +32928,7 @@
       </c>
       <c r="AG264" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -33051,7 +33051,7 @@
       </c>
       <c r="AG265" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="AG266" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -33297,7 +33297,7 @@
       </c>
       <c r="AG267" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="AG268" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>
@@ -33543,7 +33543,7 @@
       </c>
       <c r="AG269" t="inlineStr">
         <is>
-          <t>20/02/2026 07:06:55</t>
+          <t>20/02/2026 10:28:30</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2025/despesas_202512.xlsx
+++ b/base_despesas/2025/despesas_202512.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E83 - Realização do Evento Canto pela Paz, incluído no Calendário Oficial da Cidade pela Lei n. 17.0</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -8702,7 +8702,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2811 - Elaboração e Distribuição de Material para Informação de Jovens sobre Redução de Danos - Ins</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2067 - Reforma, Requalificação e Aquisição de Equipamentos para o Hospital do Servidor Público Muni</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11362,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -13357,7 +13357,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -13756,7 +13756,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t xml:space="preserve">E237 - Aquisição de Veículo Blindado de Transporte Pessoal para a Guarda Civil Metropolitana, com o </t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2223 - Intervenção, Urbanização e Melhorias de Bairro no âmbito da Subprefeitura de Itaquera</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -15485,7 +15485,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -15618,7 +15618,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16682,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -17879,7 +17879,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18677,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -18790,7 +18790,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E230 - Saúde da Mulher</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t xml:space="preserve">E2818 - Acolhimento, Apoio e Capacitação de Mulheres Vítimas de Violência em 5 Delegacias da Mulher </t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2837 - Formação e Produção de Material sobre o Sistema de Garantia de Direitos da Criança e do Adol</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -19076,7 +19076,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -19874,7 +19874,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -20007,7 +20007,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20140,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21204,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -21470,7 +21470,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -21736,7 +21736,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -21869,7 +21869,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -22135,7 +22135,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -22268,7 +22268,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -22401,7 +22401,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -22667,7 +22667,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22800,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -22933,7 +22933,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -23199,7 +23199,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -23332,7 +23332,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -23465,7 +23465,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -23598,7 +23598,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -23731,7 +23731,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -23864,7 +23864,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -24130,7 +24130,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -24263,7 +24263,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -24396,7 +24396,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -24529,7 +24529,7 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -24928,7 +24928,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -25061,7 +25061,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -25194,7 +25194,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -25327,7 +25327,7 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -25460,7 +25460,7 @@
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -25593,7 +25593,7 @@
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -25992,7 +25992,7 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -26125,7 +26125,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -26258,7 +26258,7 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -26391,7 +26391,7 @@
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -26524,7 +26524,7 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -26657,7 +26657,7 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -26790,7 +26790,7 @@
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -26923,7 +26923,7 @@
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -27056,7 +27056,7 @@
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -27189,7 +27189,7 @@
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -27322,7 +27322,7 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27455,7 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -27588,7 +27588,7 @@
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -27721,7 +27721,7 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -27834,7 +27834,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2805 - Realização de Oficinas de Formulação e Implementação de Políticas Públicas de Saúde frente a</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -27854,7 +27854,7 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -27967,7 +27967,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t xml:space="preserve">E2042 - Formação Elaboração de Materiais Ligada a Saúde Básica e Mental para Associação Paulista de </t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -27987,7 +27987,7 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28100,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2919 - Readequação de Estrutura CAPS AD III Penha</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -28233,7 +28233,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2825 - Oficinas de Formação Direitos Humanos, Cultura e Redução de Danos - Projeto Redução de Danos</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -28253,7 +28253,7 @@
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t xml:space="preserve">E2834 - Oficinas e Atividades de Acolhimento de Mulheres em Situação de Vulnerabilidade - Instituto </t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -28386,7 +28386,7 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -28499,7 +28499,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E56 - Contratação de Empresa de Engenharia ou Arquitetura para Readequação de Área Pública Municipal</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -28519,7 +28519,7 @@
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -28632,7 +28632,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E3345 - Realização de Atividades voltadas para Políticas de Redução de Danos - É de lei</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -28652,7 +28652,7 @@
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -28765,7 +28765,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E3541 - Programa Meu Trampo</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -28785,7 +28785,7 @@
       </c>
       <c r="AI213" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -28918,7 +28918,7 @@
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -29051,7 +29051,7 @@
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -29184,7 +29184,7 @@
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -29317,7 +29317,7 @@
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -29450,7 +29450,7 @@
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -29583,7 +29583,7 @@
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -29716,7 +29716,7 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -29849,7 +29849,7 @@
       </c>
       <c r="AI221" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -29982,7 +29982,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -30115,7 +30115,7 @@
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -30248,7 +30248,7 @@
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -30361,7 +30361,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2905 - Estrutura para o "Festival Consciência Continua - Coletivo Oeste RAP". Organização: Associaç</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -30381,7 +30381,7 @@
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -30494,7 +30494,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E2922 - Eventos</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -30514,7 +30514,7 @@
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -30627,7 +30627,7 @@
       </c>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E301 - Mobiliário - CAPS Vila Prudente Adulto - Praça Santa Helena, 56 - Vila Prudente, 03138-030</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -30647,7 +30647,7 @@
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -30760,7 +30760,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t xml:space="preserve">E305 - Materiais e Equipamentos para CECCO Vila Prudente - Av. Francisco Falconi, 81 - Vila Alpina, </t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -30780,7 +30780,7 @@
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -30893,7 +30893,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E3514 - Ampliação do Programa da Rede Socioassistencial para Moradores em Situação de Rua</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -31026,7 +31026,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E3342 - Realização de Formação e Oficinas em Saúde Mental para Pessoas no Território do Grajaú - Ass</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -31046,7 +31046,7 @@
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -31179,7 +31179,7 @@
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -31312,7 +31312,7 @@
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -31445,7 +31445,7 @@
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31578,7 @@
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -31844,7 +31844,7 @@
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -32110,7 +32110,7 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -32243,7 +32243,7 @@
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -32376,7 +32376,7 @@
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -32509,7 +32509,7 @@
       </c>
       <c r="AI241" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -32642,7 +32642,7 @@
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -32775,7 +32775,7 @@
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -32908,7 +32908,7 @@
       </c>
       <c r="AI244" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -33041,7 +33041,7 @@
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -33174,7 +33174,7 @@
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -33287,7 +33287,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E3514 - Cozinha Escola na Periferia</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -33307,7 +33307,7 @@
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>Emenda</t>
+          <t>E3514 - Cozinha Cidadã</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -33573,7 +33573,7 @@
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -33706,7 +33706,7 @@
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -33839,7 +33839,7 @@
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -33972,7 +33972,7 @@
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -34105,7 +34105,7 @@
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -34238,7 +34238,7 @@
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -34371,7 +34371,7 @@
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -34504,7 +34504,7 @@
       </c>
       <c r="AI256" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -34770,7 +34770,7 @@
       </c>
       <c r="AI258" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -34903,7 +34903,7 @@
       </c>
       <c r="AI259" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -35036,7 +35036,7 @@
       </c>
       <c r="AI260" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -35169,7 +35169,7 @@
       </c>
       <c r="AI261" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -35302,7 +35302,7 @@
       </c>
       <c r="AI262" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -35435,7 +35435,7 @@
       </c>
       <c r="AI263" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -35568,7 +35568,7 @@
       </c>
       <c r="AI264" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -35701,7 +35701,7 @@
       </c>
       <c r="AI265" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -35834,7 +35834,7 @@
       </c>
       <c r="AI266" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -35967,7 +35967,7 @@
       </c>
       <c r="AI267" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -36100,7 +36100,7 @@
       </c>
       <c r="AI268" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
@@ -36233,7 +36233,7 @@
       </c>
       <c r="AI269" t="inlineStr">
         <is>
-          <t>02/03/2026 14:28:00</t>
+          <t>03/03/2026 11:56:36</t>
         </is>
       </c>
     </row>
